--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260423_204326.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260423_204326.xlsx
@@ -5556,7 +5556,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5766,7 +5766,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5980,7 +5980,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6190,7 +6190,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260423_204326.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260423_204326.xlsx
@@ -5556,7 +5556,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5766,7 +5766,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5980,7 +5980,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6190,7 +6190,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
